--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488115_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488115_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.45</v>
+        <v>3.2619</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2838</v>
+        <v>4.2922</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8338</v>
+        <v>-1.0304</v>
       </c>
       <c r="G2" t="n">
         <v>4.5227</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>3.114</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0251</v>
+        <v>1.0335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.1076</v>
       </c>
       <c r="V2" t="n">
         <v>-2.5832</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5312</v>
+        <v>3.1734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4126</v>
+        <v>2.7848</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1186</v>
+        <v>0.3886</v>
       </c>
       <c r="G3" t="n">
         <v>1.2175</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2626</v>
+        <v>0.9048</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5492</v>
+        <v>0.9215</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7133</v>
+        <v>-0.0167</v>
       </c>
       <c r="V3" t="n">
         <v>1.2494</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5478</v>
+        <v>2.3056</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2866</v>
+        <v>2.1847</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2612</v>
+        <v>0.1208</v>
       </c>
       <c r="G4" t="n">
         <v>1.2759</v>
@@ -766,13 +766,13 @@
         <v>0.3964</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.6332</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5543</v>
+        <v>0.4525</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3211</v>
+        <v>0.1807</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BAMADU</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.713</v>
+        <v>-0.0018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1209</v>
+        <v>-0.5518</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8338</v>
+        <v>0.55</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8128</v>
+        <v>1.3634</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2165</v>
+        <v>-0.412</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0293</v>
+        <v>1.7753</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209</v>
+        <v>0.1855</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1816</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>0.0039</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9337</v>
+        <v>1.1779</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1358</v>
+        <v>-0.5936</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0695</v>
+        <v>1.7714</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0984</v>
+        <v>0.9103</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0128</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0984</v>
+        <v>0.923</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8065</v>
+        <v>-0.2909</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4126</v>
+        <v>-0.1687</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6062</v>
+        <v>-0.1222</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3634</v>
+        <v>0.2214</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.412</v>
+        <v>-2.4129</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7753</v>
+        <v>2.6344</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1855</v>
+        <v>1.076</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1816</v>
+        <v>-1.2297</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0039</v>
+        <v>2.3057</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1779</v>
+        <v>-0.8545</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5936</v>
+        <v>-1.1832</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7714</v>
+        <v>0.3287</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1982</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1056</v>
+        <v>0.5486</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8736</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9792</v>
+        <v>-0.0939</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0772</v>
+        <v>1.5159</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>2.0772</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3438</v>
+        <v>-0.5613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>M. BAMADU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8109</v>
+        <v>-0.4531</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2956</v>
+        <v>0.3246</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5153</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2214</v>
+        <v>-0.8128</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4129</v>
+        <v>0.2165</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6344</v>
+        <v>-1.0293</v>
       </c>
       <c r="J8" t="n">
-        <v>1.076</v>
+        <v>0.1209</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2297</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3057</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8545</v>
+        <v>-0.9337</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1832</v>
+        <v>0.1358</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3287</v>
+        <v>-1.0695</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5769</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9714</v>
+        <v>0.1615</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4844</v>
+        <v>0.2037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.487</v>
+        <v>-0.0422</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5159</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6605</v>
+        <v>-2.3871</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.703</v>
+        <v>-0.5843</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0425</v>
+        <v>-1.8028</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7287</v>
+        <v>-1.3292</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7476</v>
+        <v>-0.2042</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0189</v>
+        <v>-1.125</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0492</v>
+        <v>0.0002</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4906</v>
+        <v>0.599</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5586</v>
+        <v>-0.5988</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6795</v>
+        <v>-1.3294</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.257</v>
+        <v>-0.8032</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5775</v>
+        <v>-0.5262</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
         <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>1.317</v>
+        <v>0.4158</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3196</v>
+        <v>0.4066</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1897</v>
+        <v>-2.5065</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2184</v>
+        <v>-3.4929</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9713</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3292</v>
+        <v>-1.7287</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2042</v>
+        <v>-1.7476</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.125</v>
+        <v>0.0189</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002</v>
+        <v>-1.0492</v>
       </c>
       <c r="K10" t="n">
-        <v>0.599</v>
+        <v>-0.4906</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5988</v>
+        <v>-0.5586</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3294</v>
+        <v>-0.6795</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8032</v>
+        <v>-1.257</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5262</v>
+        <v>0.5775</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3869</v>
+        <v>1.471</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2275</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1593</v>
+        <v>0.9413</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4737</v>
+        <v>-0.2666</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4737</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6671</v>
+        <v>-5.0796</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2455</v>
+        <v>-2.8546</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4216</v>
+        <v>-2.225</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1226</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0854</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0586</v>
+        <v>0.3323</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6143</v>
+        <v>-0.4177</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8983</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.1771</v>
+        <v>-11.6457</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.731</v>
+        <v>-10.5645</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4461</v>
+        <v>-1.0811</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0799</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8564</v>
+        <v>-0.325</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0497</v>
+        <v>0.1167</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8067</v>
+        <v>-0.4417</v>
       </c>
       <c r="V12" t="n">
         <v>2.6526</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.1931</v>
+        <v>-13.3211</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.1995</v>
+        <v>-8.327800000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.9934</v>
+        <v>-4.993399999999999</v>
       </c>
       <c r="G13" t="n">
         <v>1.8304</v>
@@ -1447,7 +1447,7 @@
         <v>7.9338</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5008</v>
+        <v>-1.500800000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-4.602399999999999</v>
@@ -1468,13 +1468,13 @@
         <v>8.92</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6887</v>
+        <v>5.5607</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7544</v>
+        <v>4.6263</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9342999999999997</v>
+        <v>0.9343000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8811</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4818</v>
+        <v>7.9264</v>
       </c>
       <c r="E14" t="n">
         <v>3.8538</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6279</v>
+        <v>4.0726</v>
       </c>
       <c r="G14" t="n">
         <v>2.75</v>
@@ -1546,13 +1546,13 @@
         <v>3.3698</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0017</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-0.6202</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3815</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.3547</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0527</v>
+        <v>7.5634</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3476</v>
+        <v>5.755</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7051</v>
+        <v>1.8083</v>
       </c>
       <c r="G15" t="n">
         <v>2.3118</v>
@@ -1624,13 +1624,13 @@
         <v>3.1716</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8428</v>
+        <v>-0.3322</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3485</v>
+        <v>0.0589</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4943</v>
+        <v>-0.3911</v>
       </c>
       <c r="V15" t="n">
         <v>2.6104</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7413</v>
+        <v>2.9009</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9357</v>
+        <v>0.3245</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8055</v>
+        <v>2.5764</v>
       </c>
       <c r="G16" t="n">
         <v>0.3967</v>
@@ -1702,13 +1702,13 @@
         <v>3.1716</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7588</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2903</v>
+        <v>-0.321</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4685</v>
+        <v>0.2393</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7448</v>
+        <v>1.2237</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0074</v>
+        <v>0.2943</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.9294</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8058</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1056</v>
+        <v>-0.6267</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5581</v>
+        <v>-0.155</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4718</v>
       </c>
       <c r="V17" t="n">
         <v>0.674</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.0978</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3785</v>
+        <v>0.8878</v>
       </c>
       <c r="F18" t="n">
-        <v>0.617</v>
+        <v>0.21</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3025</v>
@@ -1858,13 +1858,13 @@
         <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9172</v>
+        <v>1.0196</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.11</v>
+        <v>0.3994</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0272</v>
+        <v>0.6202</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4033</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5105</v>
+        <v>0.2646</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8047</v>
+        <v>-0.1934</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2941</v>
+        <v>0.458</v>
       </c>
       <c r="G19" t="n">
         <v>-1.458</v>
@@ -1936,13 +1936,13 @@
         <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.233</v>
+        <v>-0.4579</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6643</v>
+        <v>-0.0531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5687</v>
+        <v>-0.4048</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9908</v>
+        <v>-0.3809</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3459</v>
+        <v>0.6515</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3367</v>
+        <v>-1.0324</v>
       </c>
       <c r="G20" t="n">
         <v>1.1206</v>
@@ -2014,13 +2014,13 @@
         <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1709</v>
+        <v>-1.561</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1121</v>
+        <v>-0.8065</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0588</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.337</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3954</v>
+        <v>-2.433</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9128</v>
+        <v>-3.339</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5174</v>
+        <v>0.906</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0698</v>
@@ -2092,13 +2092,13 @@
         <v>2.9733</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8132</v>
+        <v>0.7756</v>
       </c>
       <c r="T21" t="n">
-        <v>2.357</v>
+        <v>0.9308</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5438</v>
+        <v>-0.1552</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3028</v>
+        <v>-3.9234</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2676</v>
+        <v>-2.8602</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0351</v>
+        <v>-1.0632</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0885</v>
@@ -2170,13 +2170,13 @@
         <v>2.9733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3086</v>
+        <v>0.0708</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1724</v>
+        <v>0.2351</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1363</v>
+        <v>-0.1644</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6808</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>13.8166</v>
+        <v>14.2395</v>
       </c>
       <c r="E23" t="n">
-        <v>5.883799999999999</v>
+        <v>5.374300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>7.932599999999999</v>
+        <v>8.865100000000002</v>
       </c>
       <c r="G23" t="n">
         <v>-2.145499999999999</v>
@@ -2248,13 +2248,13 @@
         <v>25.1743</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1734</v>
+        <v>-1.7504</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1779000000000003</v>
+        <v>-0.3316000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.3515</v>
+        <v>-1.4191</v>
       </c>
       <c r="V23" t="n">
         <v>1.8811</v>
